--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126531624</v>
+        <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759173</v>
+        <v>759116</v>
       </c>
       <c r="R3" t="n">
-        <v>7202057</v>
+        <v>7202188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126531627</v>
+        <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759116</v>
+        <v>759173</v>
       </c>
       <c r="R4" t="n">
-        <v>7202188</v>
+        <v>7202057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126531615</v>
+        <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>91263</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
         <v>759153</v>
       </c>
       <c r="R15" t="n">
-        <v>7202048</v>
+        <v>7202046</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126531604</v>
+        <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>91337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
         <v>759153</v>
       </c>
       <c r="R16" t="n">
-        <v>7202046</v>
+        <v>7202048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126531518</v>
+        <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91245</v>
+        <v>91337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759158</v>
+        <v>759109</v>
       </c>
       <c r="R17" t="n">
-        <v>7202231</v>
+        <v>7202131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126531616</v>
+        <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>91263</v>
+        <v>98457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759109</v>
+        <v>759234</v>
       </c>
       <c r="R18" t="n">
-        <v>7202131</v>
+        <v>7201983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126531542</v>
+        <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>98382</v>
+        <v>91319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759234</v>
+        <v>759158</v>
       </c>
       <c r="R19" t="n">
-        <v>7201983</v>
+        <v>7202231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,6 +2419,302 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128504576</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>759187</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7202174</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128504578</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>759276</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7202109</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128504577</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>759198</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7202170</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2518,7 +2518,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128504578</v>
+        <v>128504577</v>
       </c>
       <c r="B21" t="n">
         <v>98571</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759276</v>
+        <v>759198</v>
       </c>
       <c r="R21" t="n">
-        <v>7202109</v>
+        <v>7202170</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2589,6 +2589,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128504577</v>
+        <v>128504578</v>
       </c>
       <c r="B22" t="n">
         <v>98571</v>
@@ -2650,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759198</v>
+        <v>759276</v>
       </c>
       <c r="R22" t="n">
-        <v>7202170</v>
+        <v>7202109</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2686,11 +2691,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2424,7 +2424,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>80225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80018</v>
+        <v>80129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1273,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,14 +1374,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,14 +1475,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,14 +1576,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91337</v>
+        <v>91522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,14 +1677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,14 +1778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,14 +1879,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,14 +1980,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,14 +2081,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91337</v>
+        <v>91522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,14 +2182,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91337</v>
+        <v>91522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2223,14 +2283,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98457</v>
+        <v>98653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2320,14 +2384,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,7 +2485,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80129</v>
+        <v>80133</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128504577</v>
+        <v>128504578</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759198</v>
+        <v>759276</v>
       </c>
       <c r="R21" t="n">
-        <v>7202170</v>
+        <v>7202109</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,11 +2661,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2692,10 +2687,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128504578</v>
+        <v>128504577</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,10 +2722,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759276</v>
+        <v>759198</v>
       </c>
       <c r="R22" t="n">
-        <v>7202109</v>
+        <v>7202170</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,6 +2758,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2590,7 +2590,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128504578</v>
+        <v>128504577</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759276</v>
+        <v>759198</v>
       </c>
       <c r="R21" t="n">
-        <v>7202109</v>
+        <v>7202170</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2661,6 +2661,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2687,7 +2692,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128504577</v>
+        <v>128504578</v>
       </c>
       <c r="B22" t="n">
         <v>98636</v>
@@ -2722,10 +2727,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759198</v>
+        <v>759276</v>
       </c>
       <c r="R22" t="n">
-        <v>7202170</v>
+        <v>7202109</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2758,11 +2763,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80133</v>
+        <v>80038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -2496,7 +2496,7 @@
         <v>128504576</v>
       </c>
       <c r="B20" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>128504577</v>
       </c>
       <c r="B21" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128504578</v>
       </c>
       <c r="B22" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80043</v>
+        <v>80044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,14 +1604,10 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1789,7 +1785,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1987,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2088,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,14 +2105,10 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2193,7 +2185,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2210,14 +2202,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2294,7 +2282,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98739</v>
+        <v>98740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98740</v>
+        <v>98744</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126531627</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126531624</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126531573</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126531556</v>
       </c>
       <c r="B7" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>126531625</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98744</v>
+        <v>98746</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>126531629</v>
       </c>
       <c r="B14" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 9059-2021 artfynd.xlsx
+++ b/artfynd/A 9059-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126531605</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126531602</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126531506</v>
       </c>
       <c r="B8" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>126531520</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>126531515</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>126531613</v>
       </c>
       <c r="B11" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126531570</v>
       </c>
       <c r="B13" t="n">
-        <v>98746</v>
+        <v>98750</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>126531604</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>126531615</v>
       </c>
       <c r="B16" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>126531616</v>
       </c>
       <c r="B17" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>126531542</v>
       </c>
       <c r="B18" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>126531518</v>
       </c>
       <c r="B19" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
